--- a/docs/DealGapIQ_Financial_Proforma.xlsx
+++ b/docs/DealGapIQ_Financial_Proforma.xlsx
@@ -10,11 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Costs" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Capacity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-Month Projection" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Year Projection" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Optimization" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scaling Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Capacity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-Month Projection" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Year Projection" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Optimization" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,12 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="$0.000"/>
-    <numFmt numFmtId="168" formatCode="$#,##0.00;[Red]($#,##0.00)"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00;[Red]($#,##0.00)"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -145,14 +145,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -163,8 +163,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-        <bgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -244,37 +244,37 @@
     <xf numFmtId="164" fontId="11" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="14" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="11" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -379,7 +379,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Profitability'!I15</f>
+              <f>'Profitability'!I6</f>
             </strRef>
           </tx>
           <spPr>
@@ -389,12 +389,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Profitability'!$A$16:$A$32</f>
+              <f>'Profitability'!$A$8:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Profitability'!$I$16:$I$32</f>
+              <f>'Profitability'!$I$7:$I$28</f>
             </numRef>
           </val>
         </ser>
@@ -477,21 +477,22 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Operating Margin %</a:t>
+              <a:t>Cost Composition by Subscriber Count</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Profitability'!J15</f>
+              <f>'Profitability'!D6</f>
             </strRef>
           </tx>
           <spPr>
@@ -499,28 +500,93 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Profitability'!$A$16:$A$32</f>
+              <f>'Profitability'!$A$8:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Profitability'!$J$16:$J$32</f>
+              <f>'Profitability'!$D$7:$D$28</f>
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Profitability'!E6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Profitability'!$A$8:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profitability'!$E$7:$E$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Profitability'!F6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Profitability'!$A$8:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profitability'!$F$7:$F$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Profitability'!G6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Profitability'!$A$8:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profitability'!$G$7:$G$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -563,13 +629,12 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Margin</a:t>
+                  <a:t>$ / Month</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -643,7 +708,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'12-Month Projection'!A19</f>
+              <f>'12-Month Projection'!A22</f>
             </strRef>
           </tx>
           <spPr>
@@ -666,7 +731,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'12-Month Projection'!$B$19:$M$19</f>
+              <f>'12-Month Projection'!$B$22:$M$22</f>
             </numRef>
           </val>
         </ser>
@@ -720,13 +785,183 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Monthly Cost Composition</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'12-Month Projection'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'12-Month Projection'!$B$8:$M$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'12-Month Projection'!$B$16:$M$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'12-Month Projection'!A17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'12-Month Projection'!$B$8:$M$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'12-Month Projection'!$B$17:$M$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'12-Month Projection'!A18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'12-Month Projection'!$B$8:$M$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'12-Month Projection'!$B$18:$M$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'12-Month Projection'!A19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'12-Month Projection'!$B$8:$M$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'12-Month Projection'!$B$19:$M$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$ / Month</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10080000" cy="5040000"/>
@@ -748,7 +983,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10080000" cy="5040000"/>
@@ -775,7 +1010,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10080000" cy="5040000"/>
@@ -788,6 +1023,28 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10080000" cy="5040000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1132,12 +1389,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>$386.83</t>
+          <t>$70.83</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>12 Pro</t>
+          <t>3 Pro</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1167,7 +1424,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1177,7 +1434,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>~80–200 subs</t>
+          <t>~48–80 subs</t>
         </is>
       </c>
     </row>
@@ -1469,17 +1726,17 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Fixed Monthly Costs — Current Plans</t>
+          <t>Baseline Monthly Costs — Current Plans (0 Subscribers)</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1754,22 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Monthly Cost</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Included Quota</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>Overage Rate</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -1532,25 +1789,25 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>199</v>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
+          <t>Data API</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>5,000 req/mo</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>$0.03/req</t>
-        </is>
-      </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Primary data provider</t>
+          <t>$0.03/req overage</t>
         </is>
       </c>
     </row>
@@ -1560,25 +1817,25 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Zillow / AXESSO API</t>
+          <t>Zillow / AXESSO</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>82</v>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
+          <t>Data API</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Free Trial</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>100,000 req/mo</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -1598,25 +1855,25 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Pro</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>~1,000+ req/mo</t>
-        </is>
+          <t>Data API</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>~1,000 req/mo</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Verify quota in dashboard</t>
+          <t>Verify quota</t>
         </is>
       </c>
     </row>
@@ -1631,25 +1888,25 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Pro</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>~1,000+ req/mo</t>
-        </is>
+          <t>Data API</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>~1,000 req/mo</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Verify quota in dashboard</t>
+          <t>Verify quota</t>
         </is>
       </c>
     </row>
@@ -1664,20 +1921,20 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
           <t>Pro</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="E8" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>$20 usage credit</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Usage-based</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1697,20 +1954,20 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
           <t>Pro</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="E9" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Standard limits</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Usage-based</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -1730,20 +1987,20 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
           <t>Starter</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="E10" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>3K MAUs</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1763,16 +2020,16 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="E11" s="13" t="n">
         <v>8.25</v>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
@@ -1791,21 +2048,21 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Google Play Developer</t>
+          <t>Google Play Dev</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
           <t>One-time</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="E12" s="11" t="n">
         <v>2.08</v>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1824,21 +2081,21 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Domain (dealgapiq.com)</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="E13" s="13" t="n">
         <v>1.5</v>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
@@ -1862,25 +2119,25 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
           <t>Pay-per-use</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>~$0.01/call</t>
-        </is>
-      </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Appraisal narratives</t>
+          <t>~$0.01/narrative</t>
         </is>
       </c>
     </row>
@@ -1890,30 +2147,30 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Google Maps Platform</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
           <t>Pay-as-you-go</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="E15" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>$200/mo free credit</t>
-        </is>
-      </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Pay-as-you-go</t>
+          <t>$200/mo free</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Autocomplete + Geocoding</t>
+          <t>Autocomplete + Geo</t>
         </is>
       </c>
     </row>
@@ -1928,20 +2185,20 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="E16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>5K errors/mo</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -1961,20 +2218,20 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="E17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>3,000 emails/mo</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -1994,41 +2251,41 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="E18" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>&lt; $2,500 MTR</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>1% above</t>
-        </is>
-      </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Mobile IAP management</t>
+          <t>1% above threshold</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr"/>
+      <c r="A19" s="16" t="n"/>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>TOTAL FIXED COSTS</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr"/>
-      <c r="D19" s="18">
-        <f>SUM(D4:D18)</f>
+          <t>TOTAL BASELINE</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="18">
+        <f>SUM(E4:E18)</f>
         <v/>
       </c>
-      <c r="E19" s="16" t="n"/>
       <c r="F19" s="16" t="n"/>
       <c r="G19" s="16" t="n"/>
     </row>
@@ -2036,7 +2293,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Additional Costs to Consider (Not in Total)</t>
+          <t>Additional Costs to Consider (Not in Baseline)</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2307,7 @@
       <c r="C22" s="9" t="inlineStr"/>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Est. Monthly Cost</t>
+          <t>Est. Monthly</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr"/>
@@ -2224,881 +2481,804 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Profitability by Subscriber Count</t>
+          <t>Profitability by Subscriber Count (Auto-Scaled Costs)</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>MODEL ASSUMPTIONS</t>
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>All costs computed by the centralized cost engine. Provider plans</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>Blended Net ARPU</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="n">
+          <t>auto-upgrade when volume exceeds quota. See 'Scaling Detail' sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Paid Subs</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Active (60%)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Net Revenue</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Data APIs</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>AI &amp; Variable</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Fixed Overhead</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Total Costs</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Profit/Loss</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>70.83</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>-70.83</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13" t="n">
         <v>34.12</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Activity Rate</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Searches/Active Sub/Mo</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n">
+      <c r="D8" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>-52.86000000000001</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>-1.549237983587339</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>102.48</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>68.11999999999999</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0.3992966002344666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>341.2</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>158.13</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>183.07</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>0.5365474794841735</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>409.4399999999999</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>234.21</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>0.5720252051582649</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Cache Hit Rate</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Cold Searches/Active Sub</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="n">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>RentCast Calls/Search</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>RentCast Calls/Active Sub/Mo</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Fixed Costs/Month</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="n">
-        <v>386.83</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Anthropic $/Narrative</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14"/>
+      <c r="B12" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>511.8</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>183.78</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>328.02</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>0.6409144196951935</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>852.9999999999999</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>193.08</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>659.9199999999998</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>0.7736459554513481</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>1706</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>210.93</v>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>1495.07</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>0.8763599062133646</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Paid Subs</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Active (60%)</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Gross Revenue</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Net Revenue</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Fixed Costs</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>RentCast Overage</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Total Costs</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Monthly Profit/Loss</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Operating Margin</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>2559</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>173.4</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>250.98</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>2308.02</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>0.9019226260257913</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="26">
-        <f>A16*$B$5</f>
-        <v/>
-      </c>
-      <c r="C16" s="11">
-        <f>A16*36.99</f>
-        <v/>
-      </c>
-      <c r="D16" s="11">
-        <f>A16*$B$4</f>
-        <v/>
-      </c>
-      <c r="E16" s="11">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F16" s="11">
-        <f>MAX(0, B16*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>B16*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H16" s="11">
-        <f>E16+F16+G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="27">
-        <f>D16-H16</f>
-        <v/>
-      </c>
-      <c r="J16" s="15">
-        <f>IF(D16&gt;0, I16/D16, 0)</f>
-        <v/>
+      <c r="A16" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>3412</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>281.2</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>361.03</v>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>3050.969999999999</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>0.8941881594372801</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="28">
-        <f>A17*$B$5</f>
-        <v/>
-      </c>
-      <c r="C17" s="13">
-        <f>A17*36.99</f>
-        <v/>
-      </c>
-      <c r="D17" s="13">
-        <f>A17*$B$4</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F17" s="13">
-        <f>MAX(0, B17*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G17" s="13">
-        <f>B17*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H17" s="13">
-        <f>E17+F17+G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="29">
-        <f>D17-H17</f>
-        <v/>
-      </c>
-      <c r="J17" s="14">
-        <f>IF(D17&gt;0, I17/D17, 0)</f>
-        <v/>
+      <c r="A17" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>90</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>5118</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>315</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>399.33</v>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>4718.67</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>0.9219753810082063</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="26">
-        <f>A18*$B$5</f>
-        <v/>
-      </c>
-      <c r="C18" s="11">
-        <f>A18*36.99</f>
-        <v/>
-      </c>
-      <c r="D18" s="11">
-        <f>A18*$B$4</f>
-        <v/>
-      </c>
-      <c r="E18" s="11">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F18" s="11">
-        <f>MAX(0, B18*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G18" s="11">
-        <f>B18*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H18" s="11">
-        <f>E18+F18+G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="27">
-        <f>D18-H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="15">
-        <f>IF(D18&gt;0, I18/D18, 0)</f>
-        <v/>
+      <c r="A18" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>6823.999999999999</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>239</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>585.03</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>6238.969999999999</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0.9142687573270809</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="28">
-        <f>A19*$B$5</f>
-        <v/>
-      </c>
-      <c r="C19" s="13">
-        <f>A19*36.99</f>
-        <v/>
-      </c>
-      <c r="D19" s="13">
-        <f>A19*$B$4</f>
-        <v/>
-      </c>
-      <c r="E19" s="13">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F19" s="13">
-        <f>MAX(0, B19*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G19" s="13">
-        <f>B19*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H19" s="13">
-        <f>E19+F19+G19</f>
-        <v/>
-      </c>
-      <c r="I19" s="30">
-        <f>D19-H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="14">
-        <f>IF(D19&gt;0, I19/D19, 0)</f>
-        <v/>
+      <c r="A19" s="21" t="n">
+        <v>250</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>8530</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>354</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>269</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>657.33</v>
+      </c>
+      <c r="I19" s="25" t="n">
+        <v>7872.67</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>0.9229390386869871</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="26">
-        <f>A20*$B$5</f>
-        <v/>
-      </c>
-      <c r="C20" s="11">
-        <f>A20*36.99</f>
-        <v/>
-      </c>
-      <c r="D20" s="11">
-        <f>A20*$B$4</f>
-        <v/>
-      </c>
-      <c r="E20" s="11">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F20" s="11">
-        <f>MAX(0, B20*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G20" s="11">
-        <f>B20*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H20" s="11">
-        <f>E20+F20+G20</f>
-        <v/>
-      </c>
-      <c r="I20" s="31">
-        <f>D20-H20</f>
-        <v/>
-      </c>
-      <c r="J20" s="15">
-        <f>IF(D20&gt;0, I20/D20, 0)</f>
-        <v/>
+      <c r="A20" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>180</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>10236</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>391.8</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>269</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>699.63</v>
+      </c>
+      <c r="I20" s="26" t="n">
+        <v>9536.370000000001</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0.9316500586166472</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B21" s="28">
-        <f>A21*$B$5</f>
-        <v/>
-      </c>
-      <c r="C21" s="13">
-        <f>A21*36.99</f>
-        <v/>
-      </c>
-      <c r="D21" s="13">
-        <f>A21*$B$4</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F21" s="13">
-        <f>MAX(0, B21*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G21" s="13">
-        <f>B21*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H21" s="13">
-        <f>E21+F21+G21</f>
-        <v/>
-      </c>
-      <c r="I21" s="30">
-        <f>D21-H21</f>
-        <v/>
-      </c>
-      <c r="J21" s="14">
-        <f>IF(D21&gt;0, I21/D21, 0)</f>
-        <v/>
+      <c r="A21" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>240</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>13648</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>567.4</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>269</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>888.8200000000001</v>
+      </c>
+      <c r="I21" s="25" t="n">
+        <v>12759.18</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>0.9348754396248534</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="B22" s="26">
-        <f>A22*$B$5</f>
-        <v/>
-      </c>
-      <c r="C22" s="11">
-        <f>A22*36.99</f>
-        <v/>
-      </c>
-      <c r="D22" s="11">
-        <f>A22*$B$4</f>
-        <v/>
-      </c>
-      <c r="E22" s="11">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F22" s="11">
-        <f>MAX(0, B22*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G22" s="11">
-        <f>B22*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H22" s="11">
-        <f>E22+F22+G22</f>
-        <v/>
-      </c>
-      <c r="I22" s="31">
-        <f>D22-H22</f>
-        <v/>
-      </c>
-      <c r="J22" s="15">
-        <f>IF(D22&gt;0, I22/D22, 0)</f>
-        <v/>
+      <c r="A22" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>17060</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>643</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>269</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>980.8200000000001</v>
+      </c>
+      <c r="I22" s="26" t="n">
+        <v>16079.18</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>0.9425076201641266</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="B23" s="28">
-        <f>A23*$B$5</f>
-        <v/>
-      </c>
-      <c r="C23" s="13">
-        <f>A23*36.99</f>
-        <v/>
-      </c>
-      <c r="D23" s="13">
-        <f>A23*$B$4</f>
-        <v/>
-      </c>
-      <c r="E23" s="13">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F23" s="13">
-        <f>MAX(0, B23*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G23" s="13">
-        <f>B23*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H23" s="13">
-        <f>E23+F23+G23</f>
-        <v/>
-      </c>
-      <c r="I23" s="30">
-        <f>D23-H23</f>
-        <v/>
-      </c>
-      <c r="J23" s="14">
-        <f>IF(D23&gt;0, I23/D23, 0)</f>
-        <v/>
+      <c r="A23" s="21" t="n">
+        <v>750</v>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>450</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>25590</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>665</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>339</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>1113.81</v>
+      </c>
+      <c r="I23" s="25" t="n">
+        <v>24476.19</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>0.956474794841735</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="B24" s="26">
-        <f>A24*$B$5</f>
-        <v/>
-      </c>
-      <c r="C24" s="11">
-        <f>A24*36.99</f>
-        <v/>
-      </c>
-      <c r="D24" s="11">
-        <f>A24*$B$4</f>
-        <v/>
-      </c>
-      <c r="E24" s="11">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F24" s="11">
-        <f>MAX(0, B24*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G24" s="11">
-        <f>B24*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H24" s="11">
-        <f>E24+F24+G24</f>
-        <v/>
-      </c>
-      <c r="I24" s="31">
-        <f>D24-H24</f>
-        <v/>
-      </c>
-      <c r="J24" s="15">
-        <f>IF(D24&gt;0, I24/D24, 0)</f>
-        <v/>
+      <c r="A24" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>34120</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>968</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>339</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>138.98</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>1457.81</v>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>32662.19</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>0.9572740328253223</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="B25" s="28">
-        <f>A25*$B$5</f>
-        <v/>
-      </c>
-      <c r="C25" s="13">
-        <f>A25*36.99</f>
-        <v/>
-      </c>
-      <c r="D25" s="13">
-        <f>A25*$B$4</f>
-        <v/>
-      </c>
-      <c r="E25" s="13">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F25" s="13">
-        <f>MAX(0, B25*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G25" s="13">
-        <f>B25*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H25" s="13">
-        <f>E25+F25+G25</f>
-        <v/>
-      </c>
-      <c r="I25" s="30">
-        <f>D25-H25</f>
-        <v/>
-      </c>
-      <c r="J25" s="14">
-        <f>IF(D25&gt;0, I25/D25, 0)</f>
-        <v/>
+      <c r="A25" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>900</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>51179.99999999999</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>1223</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>339</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>220.97</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>1794.8</v>
+      </c>
+      <c r="I25" s="25" t="n">
+        <v>49385.19999999999</v>
+      </c>
+      <c r="J25" s="15" t="n">
+        <v>0.9649316139116841</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="B26" s="26">
-        <f>A26*$B$5</f>
-        <v/>
-      </c>
-      <c r="C26" s="11">
-        <f>A26*36.99</f>
-        <v/>
-      </c>
-      <c r="D26" s="11">
-        <f>A26*$B$4</f>
-        <v/>
-      </c>
-      <c r="E26" s="11">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F26" s="11">
-        <f>MAX(0, B26*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G26" s="11">
-        <f>B26*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H26" s="11">
-        <f>E26+F26+G26</f>
-        <v/>
-      </c>
-      <c r="I26" s="31">
-        <f>D26-H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="15">
-        <f>IF(D26&gt;0, I26/D26, 0)</f>
-        <v/>
+      <c r="A26" s="23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>68240</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>1412</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>439</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>302.96</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>2165.79</v>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>66074.21000000001</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>0.9682621629542791</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="B27" s="28">
-        <f>A27*$B$5</f>
-        <v/>
-      </c>
-      <c r="C27" s="13">
-        <f>A27*36.99</f>
-        <v/>
-      </c>
-      <c r="D27" s="13">
-        <f>A27*$B$4</f>
-        <v/>
-      </c>
-      <c r="E27" s="13">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="F27" s="13">
-        <f>MAX(0, B27*42 - 5000)*0.03</f>
-        <v/>
-      </c>
-      <c r="G27" s="13">
-        <f>B27*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H27" s="13">
-        <f>E27+F27+G27</f>
-        <v/>
-      </c>
-      <c r="I27" s="30">
-        <f>D27-H27</f>
-        <v/>
-      </c>
-      <c r="J27" s="14">
-        <f>IF(D27&gt;0, I27/D27, 0)</f>
-        <v/>
+      <c r="A27" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B27" s="21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>102360</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>1790</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>799</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>466.94</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>3067.77</v>
+      </c>
+      <c r="I27" s="25" t="n">
+        <v>99292.22999999998</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>0.9700296014067995</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B28" s="26">
-        <f>A28*$B$5</f>
-        <v/>
-      </c>
-      <c r="C28" s="11">
-        <f>A28*36.99</f>
-        <v/>
-      </c>
-      <c r="D28" s="11">
-        <f>A28*$B$4</f>
-        <v/>
-      </c>
-      <c r="E28" s="11">
-        <f>$B$11+250</f>
-        <v/>
-      </c>
-      <c r="F28" s="11">
-        <f>MAX(0, B28*42 - 25000)*0.015</f>
-        <v/>
-      </c>
-      <c r="G28" s="11">
-        <f>B28*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H28" s="11">
-        <f>E28+F28+G28</f>
-        <v/>
-      </c>
-      <c r="I28" s="31">
-        <f>D28-H28</f>
-        <v/>
-      </c>
-      <c r="J28" s="15">
-        <f>IF(D28&gt;0, I28/D28, 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B29" s="28">
-        <f>A29*$B$5</f>
-        <v/>
-      </c>
-      <c r="C29" s="13">
-        <f>A29*36.99</f>
-        <v/>
-      </c>
-      <c r="D29" s="13">
-        <f>A29*$B$4</f>
-        <v/>
-      </c>
-      <c r="E29" s="13">
-        <f>$B$11+250</f>
-        <v/>
-      </c>
-      <c r="F29" s="13">
-        <f>MAX(0, B29*42 - 25000)*0.015</f>
-        <v/>
-      </c>
-      <c r="G29" s="13">
-        <f>B29*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H29" s="13">
-        <f>E29+F29+G29</f>
-        <v/>
-      </c>
-      <c r="I29" s="30">
-        <f>D29-H29</f>
-        <v/>
-      </c>
-      <c r="J29" s="14">
-        <f>IF(D29&gt;0, I29/D29, 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>500</v>
-      </c>
-      <c r="B30" s="26">
-        <f>A30*$B$5</f>
-        <v/>
-      </c>
-      <c r="C30" s="11">
-        <f>A30*36.99</f>
-        <v/>
-      </c>
-      <c r="D30" s="11">
-        <f>A30*$B$4</f>
-        <v/>
-      </c>
-      <c r="E30" s="11">
-        <f>$B$11+250+180+40</f>
-        <v/>
-      </c>
-      <c r="F30" s="11">
-        <f>MAX(0, B30*42 - 25000)*0.015</f>
-        <v/>
-      </c>
-      <c r="G30" s="11">
-        <f>B30*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H30" s="11">
-        <f>E30+F30+G30</f>
-        <v/>
-      </c>
-      <c r="I30" s="31">
-        <f>D30-H30</f>
-        <v/>
-      </c>
-      <c r="J30" s="15">
-        <f>IF(D30&gt;0, I30/D30, 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n">
-        <v>750</v>
-      </c>
-      <c r="B31" s="28">
-        <f>A31*$B$5</f>
-        <v/>
-      </c>
-      <c r="C31" s="13">
-        <f>A31*36.99</f>
-        <v/>
-      </c>
-      <c r="D31" s="13">
-        <f>A31*$B$4</f>
-        <v/>
-      </c>
-      <c r="E31" s="13">
-        <f>$B$11+250+180+40</f>
-        <v/>
-      </c>
-      <c r="F31" s="13">
-        <f>MAX(0, B31*42 - 25000)*0.015</f>
-        <v/>
-      </c>
-      <c r="G31" s="13">
-        <f>B31*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H31" s="13">
-        <f>E31+F31+G31</f>
-        <v/>
-      </c>
-      <c r="I31" s="30">
-        <f>D31-H31</f>
-        <v/>
-      </c>
-      <c r="J31" s="14">
-        <f>IF(D31&gt;0, I31/D31, 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B32" s="26">
-        <f>A32*$B$5</f>
-        <v/>
-      </c>
-      <c r="C32" s="11">
-        <f>A32*36.99</f>
-        <v/>
-      </c>
-      <c r="D32" s="11">
-        <f>A32*$B$4</f>
-        <v/>
-      </c>
-      <c r="E32" s="11">
-        <f>$B$11+250+180+40</f>
-        <v/>
-      </c>
-      <c r="F32" s="11">
-        <f>MAX(0, B32*42 - 25000)*0.015</f>
-        <v/>
-      </c>
-      <c r="G32" s="11">
-        <f>B32*15*$B$12</f>
-        <v/>
-      </c>
-      <c r="H32" s="11">
-        <f>E32+F32+G32</f>
-        <v/>
-      </c>
-      <c r="I32" s="31">
-        <f>D32-H32</f>
-        <v/>
-      </c>
-      <c r="J32" s="15">
-        <f>IF(D32&gt;0, I32/D32, 0)</f>
-        <v/>
+      <c r="A28" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B28" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>170600</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>2806</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>799</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>878.4</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>4495.23</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>166104.77</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>0.973650468933177</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:D3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3112,736 +3292,3666 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>API Capacity &amp; Scaling Triggers</t>
+          <t>Per-Provider Cost &amp; Plan at Each Subscriber Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Plans auto-upgrade when call volume exceeds quota. Yellow = upgraded from baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Paid Subs</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>RentCast Plan</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>RentCast $</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Zillow / AXESSO Plan</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Zillow / AXESSO $</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>RapidAPI — Redfin Plan</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>RapidAPI — Redfin $</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>RapidAPI — Realtor Plan</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>RapidAPI — Realtor $</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Railway Plan</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Railway $</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>Vercel Plan</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>Vercel $</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>Expo (EAS) Plan</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>Expo (EAS) $</t>
+        </is>
+      </c>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>Anthropic (Claude) Plan</t>
+        </is>
+      </c>
+      <c r="R4" s="9" t="inlineStr">
+        <is>
+          <t>Anthropic (Claude) $</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps Plan</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps $</t>
+        </is>
+      </c>
+      <c r="U4" s="9" t="inlineStr">
+        <is>
+          <t>RevenueCat Plan</t>
+        </is>
+      </c>
+      <c r="V4" s="9" t="inlineStr">
+        <is>
+          <t>RevenueCat $</t>
+        </is>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL COST</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Free Trial</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="11" t="n">
+        <v>70.83</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R6" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="13" t="n">
+        <v>86.98</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R7" s="11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="11" t="n">
+        <v>102.48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q8" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R8" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="13" t="n">
+        <v>158.13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" s="27" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R9" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="11" t="n">
+        <v>175.23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q10" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="13" t="n">
+        <v>183.78</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R11" s="11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="11" t="n">
+        <v>193.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P12" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R12" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="13" t="n">
+        <v>210.93</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="I13" s="27" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R13" s="11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="11" t="n">
+        <v>250.98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P14" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q14" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R14" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="13" t="n">
+        <v>361.03</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>90</v>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>199</v>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" s="27" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R15" s="11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="11" t="n">
+        <v>399.33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>200.2</v>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="P16" s="13" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q16" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R16" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="13" t="n">
+        <v>585.03</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="n">
+        <v>250</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>238</v>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" s="27" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="K17" s="27" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O17" s="27" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R17" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="11" t="n">
+        <v>657.33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>180</v>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>275.8</v>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="P18" s="13" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q18" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="13" t="n">
+        <v>699.63</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>240</v>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="27" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" s="27" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O19" s="27" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="10" t="inlineStr">
+        <is>
+          <t>1% MTR</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="W19" s="11" t="n">
+        <v>888.8200000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>427</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="P20" s="13" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q20" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R20" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="12" t="inlineStr">
+        <is>
+          <t>1% MTR</t>
+        </is>
+      </c>
+      <c r="V20" s="13" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="W20" s="13" t="n">
+        <v>980.8200000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>750</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>450</v>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>449</v>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" s="27" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K21" s="27" t="inlineStr">
+        <is>
+          <t>Pro (heavy)</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M21" s="27" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="O21" s="27" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R21" s="11" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="10" t="inlineStr">
+        <is>
+          <t>1% MTR</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="W21" s="11" t="n">
+        <v>1113.81</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>452</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>Pro (heavy)</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="P22" s="13" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q22" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R22" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="12" t="inlineStr">
+        <is>
+          <t>1% MTR</t>
+        </is>
+      </c>
+      <c r="V22" s="13" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="W22" s="13" t="n">
+        <v>1457.81</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>900</v>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>641</v>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="I23" s="27" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>Pro (heavy)</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M23" s="27" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="O23" s="27" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R23" s="11" t="n">
+        <v>135</v>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="10" t="inlineStr">
+        <is>
+          <t>1% MTR</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="n">
+        <v>85.97</v>
+      </c>
+      <c r="W23" s="11" t="n">
+        <v>1794.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>830</v>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>Pro (high)</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="P24" s="13" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q24" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R24" s="13" t="n">
+        <v>180</v>
+      </c>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="12" t="inlineStr">
+        <is>
+          <t>1% MTR</t>
+        </is>
+      </c>
+      <c r="V24" s="13" t="n">
+        <v>122.96</v>
+      </c>
+      <c r="W24" s="13" t="n">
+        <v>2165.79</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>1208</v>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="G25" s="27" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="I25" s="27" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>Pro (high)</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="M25" s="27" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="O25" s="27" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>499</v>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R25" s="11" t="n">
+        <v>270</v>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="10" t="inlineStr">
+        <is>
+          <t>1% MTR</t>
+        </is>
+      </c>
+      <c r="V25" s="11" t="n">
+        <v>196.94</v>
+      </c>
+      <c r="W25" s="11" t="n">
+        <v>3067.77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>1964</v>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>Pro (high)</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="P26" s="13" t="n">
+        <v>499</v>
+      </c>
+      <c r="Q26" s="12" t="inlineStr">
+        <is>
+          <t>Pay-per-use</t>
+        </is>
+      </c>
+      <c r="R26" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="S26" s="12" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="T26" s="13" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="U26" s="12" t="inlineStr">
+        <is>
+          <t>1% MTR</t>
+        </is>
+      </c>
+      <c r="V26" s="13" t="n">
+        <v>344.9</v>
+      </c>
+      <c r="W26" s="13" t="n">
+        <v>4495.23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>API Capacity &amp; Plan Transitions</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>API CALLS PER COLD PROPERTY SEARCH</t>
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>RentCast — PLAN TIERS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
+          <t>Monthly Fee</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Included Quota</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Overage Rate</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Max Active Subs</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Max Paid Subs (60%)</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
           <t>Calls/Search</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Calls/Active Sub/Mo</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Included Quota</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Max Active Subs</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>Max Paid Subs (60%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>RentCast</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n">
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>$0.2/req</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="D5" s="26" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>119</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Zillow / AXESSO</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E6" s="28" t="n">
-        <v>6250</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>10417</v>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>74</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>$0.06/req</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Redfin (RapidAPI)</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>21</v>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>199</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>5000</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>~1,000+</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>~48+</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>~80+</t>
-        </is>
+          <t>$0.03/req</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>119</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>198</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Realtor (RapidAPI)</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>449</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>$0.015/req</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>595</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>992</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Zillow / AXESSO — PLAN TIERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Fee</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Included Quota</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Overage Rate</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Max Active Subs</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Max Paid Subs (60%)</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Calls/Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Free Trial</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>635</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>1058</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>6349</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>10582</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>164</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>19048</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>31746</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Ent. Basic</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>493</v>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>63492</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>105820</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Ent. Premium</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>877</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>$0.001/req</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>158730</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>264550</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>RapidAPI — Redfin — PLAN TIERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Fee</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Included Quota</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Overage Rate</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Max Active Subs</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Max Paid Subs (60%)</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Calls/Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>~1,000+</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>~48+</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>~80+</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="C9" s="16" t="n">
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>48</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>238</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>397</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>RENTCAST SCALING ANALYSIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Paid Subs</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Active Subs</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>RentCast Calls/Mo</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Within Growth (5K)?</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Growth Overage Cost</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>Scale Plan Cost</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Optimal Plan</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>Monthly API Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" s="26" t="n">
-        <v>294</v>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="n">
+      <c r="C24" s="23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="n">
+        <v>476</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>794</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>$0.01/req</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>2381</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>3968</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>RapidAPI — Realtor — PLAN TIERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Fee</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Included Quota</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Overage Rate</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Max Active Subs</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Max Paid Subs (60%)</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Calls/Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>449</v>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Growth ($199)</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="n">
+      <c r="C29" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>48</v>
+      </c>
+      <c r="F30" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>238</v>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>397</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C32" s="23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>n/a (must upgrade)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>476</v>
+      </c>
+      <c r="F32" s="23" t="n">
+        <v>794</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>$0.01/req</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>2381</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>3968</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>INFRASTRUCTURE SCALING TIERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Cost</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Max Paid Subs</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Railway</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D37" s="21" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Railway</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D38" s="23" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Railway</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Pro (heavy)</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Railway</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Pro (high)</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Vercel</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D41" s="21" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Vercel</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Vercel</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D43" s="21" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Expo (EAS)</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Expo (EAS)</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="n">
         <v>199</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" s="28" t="n">
-        <v>630</v>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="n">
+      <c r="D45" s="23" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Expo (EAS)</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>499</v>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>PLAN UPGRADE TRIGGER POINTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Current Plan</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Upgrade To</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Trigger (Paid Subs)</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>Cost Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Zillow / AXESSO</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Free Trial</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>~1 subs</t>
+        </is>
+      </c>
+      <c r="E50" s="29" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>RapidAPI — Redfin</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>~10 subs</t>
+        </is>
+      </c>
+      <c r="E51" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="13" t="n">
-        <v>449</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>Growth ($199)</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="C15" s="26" t="n">
-        <v>1260</v>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="n">
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>RapidAPI — Realtor</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>~10 subs</t>
+        </is>
+      </c>
+      <c r="E52" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>449</v>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Growth ($199)</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="C16" s="28" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D16" s="32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>RentCast</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>~25 subs</t>
+        </is>
+      </c>
+      <c r="E53" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="13" t="n">
-        <v>449</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>Growth ($199)</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="n">
-        <v>119</v>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="C17" s="26" t="n">
-        <v>4982</v>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>At limit</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="n">
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>RapidAPI — Redfin</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>~100 subs</t>
+        </is>
+      </c>
+      <c r="E54" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>449</v>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Growth ($199)</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="C18" s="28" t="n">
-        <v>5040</v>
-      </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>449</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>Growth ($199 + ovg)</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>200.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>7560</v>
-      </c>
-      <c r="D19" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>449</v>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Scale ($449)</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>300</v>
-      </c>
-      <c r="C20" s="28" t="n">
-        <v>12600</v>
-      </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>228</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>449</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>Scale ($449)</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>750</v>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="C21" s="26" t="n">
-        <v>18900</v>
-      </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>417</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>449</v>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Scale ($449)</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>600</v>
-      </c>
-      <c r="C22" s="28" t="n">
-        <v>25200</v>
-      </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>606</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>452</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>Scale ($449 + ovg)</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="n">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>INFRASTRUCTURE SCALING TRIGGERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Subscriber Threshold</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Monthly Cost Impact</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>~80 subs</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>RapidAPI quotas (verify)</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Upgrade Redfin + Realtor plans</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>+$20–50/mo each</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>RapidAPI — Realtor</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>~100 subs</t>
+        </is>
+      </c>
+      <c r="E55" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>RentCast</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>~150 subs</t>
+        </is>
+      </c>
+      <c r="E56" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Expo (EAS)</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>~200 subs</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>RentCast 5K limit</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Pay overage or evaluate Scale</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>+$0–250/mo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>~300 subs</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>RentCast overage &gt; Scale cost</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Upgrade to Scale ($449)</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>+$250/mo</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>~500 subs</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Railway compute scaling</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Higher resource consumption</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>+$20–80/mo</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>~500 subs</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Expo 3K MAU limit</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Upgrade to Production ($199)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>+$180/mo</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>~1,000 subs</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Vercel bandwidth/functions</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Team or Enterprise plan</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>+$20–100/mo</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>~2,500 subs</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>RevenueCat $2,500 MTR</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>1% of mobile MTR</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>~$25–100/mo</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>~5,000 subs</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Zillow 100K limit</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Upgrade to Business (€150)</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>+$82/mo</t>
-        </is>
+      <c r="E57" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Railway</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>~250 subs</t>
+        </is>
+      </c>
+      <c r="E58" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>RapidAPI — Redfin</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>~400 subs</t>
+        </is>
+      </c>
+      <c r="E59" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>RapidAPI — Realtor</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>~400 subs</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>RentCast</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>~750 subs</t>
+        </is>
+      </c>
+      <c r="E61" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Railway</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Pro (heavy)</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>~750 subs</t>
+        </is>
+      </c>
+      <c r="E62" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Vercel</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>~750 subs</t>
+        </is>
+      </c>
+      <c r="E63" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>RapidAPI — Redfin</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>~1000 subs</t>
+        </is>
+      </c>
+      <c r="E64" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>RapidAPI — Realtor</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>~1000 subs</t>
+        </is>
+      </c>
+      <c r="E65" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Zillow / AXESSO</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>~1500 subs</t>
+        </is>
+      </c>
+      <c r="E66" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>Railway</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Pro (heavy)</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Pro (high)</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>~2000 subs</t>
+        </is>
+      </c>
+      <c r="E67" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Vercel</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Pro (scaled)</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>~3000 subs</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>Expo (EAS)</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>~3000 subs</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3852,7 +6962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008B5CF6"/>
@@ -3864,9 +6974,9 @@
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3899,7 +7009,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Fixed Costs</t>
+          <t>Base Fixed Costs</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -3911,17 +7021,17 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>100% Web Monthly (best case)</t>
+          <t>100% Web Monthly (best)</t>
         </is>
       </c>
       <c r="B5" s="11" t="n">
         <v>38.53</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>386.83</v>
+        <v>70.83</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3934,10 +7044,10 @@
         <v>28.3</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>386.83</v>
+        <v>70.83</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3950,10 +7060,10 @@
         <v>34.12</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>386.83</v>
+        <v>70.83</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3966,58 +7076,58 @@
         <v>33.99</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>386.83</v>
+        <v>70.83</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>100% iOS Annual (worst case)</t>
+          <t>100% iOS Annual (worst)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>24.79</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>386.83</v>
+        <v>70.83</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Heavy mobile (40% mobile)</t>
+          <t>Heavy mobile (40%)</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
         <v>31.95</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>386.83</v>
+        <v>70.83</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Heavy annual (70% annual)</t>
+          <t>Heavy annual (70%)</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>30.24</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>386.83</v>
+        <v>70.83</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12"/>
@@ -4046,12 +7156,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Monthly Rev @ 50 Subs</t>
+          <t>Monthly Rev @ 50</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Annual Rev @ 50 Subs</t>
+          <t>Annual Rev @ 50</t>
         </is>
       </c>
     </row>
@@ -4063,7 +7173,7 @@
         <v>19.11029</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>955.5144999999998</v>
@@ -4080,7 +7190,7 @@
         <v>23.96529</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>1198.2645</v>
@@ -4097,7 +7207,7 @@
         <v>28.82029</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>1441.0145</v>
@@ -4114,7 +7224,7 @@
         <v>33.67529</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D18" s="13" t="n">
         <v>1683.7645</v>
@@ -4124,19 +7234,19 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n">
+      <c r="A19" s="30" t="n">
         <v>39.99</v>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="30" t="n">
         <v>38.53029</v>
       </c>
-      <c r="C19" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="D19" s="35" t="n">
+      <c r="C19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="30" t="n">
         <v>1926.5145</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="30" t="n">
         <v>23118.174</v>
       </c>
     </row>
@@ -4148,7 +7258,7 @@
         <v>43.38529</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D20" s="13" t="n">
         <v>2169.2645</v>
@@ -4165,7 +7275,7 @@
         <v>48.24029</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>2412.0145</v>
@@ -4182,7 +7292,7 @@
         <v>57.95029</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="n">
         <v>2897.5145</v>
@@ -4199,7 +7309,7 @@
         <v>77.37029</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>3868.5145</v>
@@ -4234,12 +7344,12 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>12-Mo Retained Subs</t>
+          <t>12-Mo Retained</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>12-Mo Cumulative Revenue</t>
+          <t>12-Mo Cumulative Rev</t>
         </is>
       </c>
     </row>
@@ -4247,13 +7357,13 @@
       <c r="A27" s="15" t="n">
         <v>0.03</v>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="32" t="n">
         <v>33.3</v>
       </c>
       <c r="C27" s="11" t="n">
         <v>1137.33</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="21" t="n">
         <v>35</v>
       </c>
       <c r="E27" s="11" t="n">
@@ -4264,13 +7374,13 @@
       <c r="A28" s="14" t="n">
         <v>0.05</v>
       </c>
-      <c r="B28" s="38" t="n">
+      <c r="B28" s="33" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>682.4</v>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D28" s="23" t="n">
         <v>27</v>
       </c>
       <c r="E28" s="13" t="n">
@@ -4281,13 +7391,13 @@
       <c r="A29" s="15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="32" t="n">
         <v>14.3</v>
       </c>
       <c r="C29" s="11" t="n">
         <v>487.43</v>
       </c>
-      <c r="D29" s="26" t="n">
+      <c r="D29" s="21" t="n">
         <v>21</v>
       </c>
       <c r="E29" s="11" t="n">
@@ -4298,13 +7408,13 @@
       <c r="A30" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="B30" s="38" t="n">
+      <c r="B30" s="33" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>341.2</v>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D30" s="23" t="n">
         <v>14</v>
       </c>
       <c r="E30" s="13" t="n">
@@ -4315,13 +7425,13 @@
       <c r="A31" s="15" t="n">
         <v>0.12</v>
       </c>
-      <c r="B31" s="37" t="n">
+      <c r="B31" s="32" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="C31" s="11" t="n">
         <v>284.33</v>
       </c>
-      <c r="D31" s="26" t="n">
+      <c r="D31" s="21" t="n">
         <v>11</v>
       </c>
       <c r="E31" s="11" t="n">
@@ -4332,13 +7442,13 @@
       <c r="A32" s="14" t="n">
         <v>0.15</v>
       </c>
-      <c r="B32" s="38" t="n">
+      <c r="B32" s="33" t="n">
         <v>6.7</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>227.47</v>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D32" s="23" t="n">
         <v>7</v>
       </c>
       <c r="E32" s="13" t="n">
@@ -4349,13 +7459,13 @@
       <c r="A33" s="15" t="n">
         <v>0.2</v>
       </c>
-      <c r="B33" s="37" t="n">
+      <c r="B33" s="32" t="n">
         <v>5</v>
       </c>
       <c r="C33" s="11" t="n">
         <v>170.6</v>
       </c>
-      <c r="D33" s="26" t="n">
+      <c r="D33" s="21" t="n">
         <v>3</v>
       </c>
       <c r="E33" s="11" t="n">
@@ -4370,14 +7480,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0022C55E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4399,7 +7509,7 @@
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>12-Month Financial Projection</t>
+          <t>12-Month Financial Projection (Auto-Scaled Costs)</t>
         </is>
       </c>
     </row>
@@ -4417,7 +7527,7 @@
           <t>Starting subscribers (Month 1)</t>
         </is>
       </c>
-      <c r="B4" s="39" t="n">
+      <c r="B4" s="34" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4427,7 +7537,7 @@
           <t>Monthly subscriber growth rate</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="35" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4437,7 +7547,7 @@
           <t>Monthly churn rate</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="35" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -4511,140 +7621,140 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>New Subscribers</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="40" t="n">
+      <c r="C9" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="40" t="n">
+      <c r="G9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="40" t="n">
+      <c r="H9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="40" t="n">
+      <c r="I9" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="40" t="n">
+      <c r="J9" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="K9" s="40" t="n">
+      <c r="K9" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="40" t="n">
+      <c r="L9" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="M9" s="40" t="n">
+      <c r="M9" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="N9" s="40" t="n">
+      <c r="N9" s="37" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Churned Subscribers</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="40" t="n">
+      <c r="C10" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="40" t="n">
+      <c r="G10" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="40" t="n">
+      <c r="H10" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="40" t="n">
+      <c r="I10" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="40" t="n">
+      <c r="J10" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="40" t="n">
+      <c r="K10" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="L10" s="40" t="n">
+      <c r="L10" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="M10" s="40" t="n">
+      <c r="M10" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="N10" s="40" t="n">
+      <c r="N10" s="37" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Ending Subscribers</t>
         </is>
       </c>
-      <c r="B11" s="42" t="n">
+      <c r="B11" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="42" t="n">
+      <c r="C11" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="42" t="n">
+      <c r="D11" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="42" t="n">
+      <c r="E11" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="42" t="n">
+      <c r="F11" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="42" t="n">
+      <c r="G11" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="H11" s="42" t="n">
+      <c r="H11" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="I11" s="42" t="n">
+      <c r="I11" s="39" t="n">
         <v>16</v>
       </c>
-      <c r="J11" s="42" t="n">
+      <c r="J11" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="K11" s="42" t="n">
+      <c r="K11" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="L11" s="42" t="n">
+      <c r="L11" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="M11" s="42" t="n">
+      <c r="M11" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="N11" s="42" t="n">
+      <c r="N11" s="39" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4652,378 +7762,469 @@
       <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Gross Revenue</t>
         </is>
       </c>
-      <c r="B13" s="43" t="n">
+      <c r="B13" s="40" t="n">
         <v>184.95</v>
       </c>
-      <c r="C13" s="43" t="n">
+      <c r="C13" s="40" t="n">
         <v>221.94</v>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="40" t="n">
         <v>258.93</v>
       </c>
-      <c r="E13" s="43" t="n">
+      <c r="E13" s="40" t="n">
         <v>295.92</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="40" t="n">
         <v>332.91</v>
       </c>
-      <c r="G13" s="43" t="n">
+      <c r="G13" s="40" t="n">
         <v>406.89</v>
       </c>
-      <c r="H13" s="43" t="n">
+      <c r="H13" s="40" t="n">
         <v>480.87</v>
       </c>
-      <c r="I13" s="43" t="n">
+      <c r="I13" s="40" t="n">
         <v>591.84</v>
       </c>
-      <c r="J13" s="43" t="n">
+      <c r="J13" s="40" t="n">
         <v>665.8200000000001</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="40" t="n">
         <v>776.79</v>
       </c>
-      <c r="L13" s="43" t="n">
+      <c r="L13" s="40" t="n">
         <v>924.75</v>
       </c>
-      <c r="M13" s="43" t="n">
+      <c r="M13" s="40" t="n">
         <v>1109.7</v>
       </c>
-      <c r="N13" s="43" t="n">
+      <c r="N13" s="40" t="n">
         <v>6251.31</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>Net Revenue</t>
         </is>
       </c>
-      <c r="B14" s="44" t="n">
+      <c r="B14" s="41" t="n">
         <v>170.6</v>
       </c>
-      <c r="C14" s="44" t="n">
+      <c r="C14" s="41" t="n">
         <v>204.72</v>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="41" t="n">
         <v>238.84</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="41" t="n">
         <v>272.96</v>
       </c>
-      <c r="F14" s="44" t="n">
+      <c r="F14" s="41" t="n">
         <v>307.08</v>
       </c>
-      <c r="G14" s="44" t="n">
+      <c r="G14" s="41" t="n">
         <v>375.32</v>
       </c>
-      <c r="H14" s="44" t="n">
+      <c r="H14" s="41" t="n">
         <v>443.56</v>
       </c>
-      <c r="I14" s="44" t="n">
+      <c r="I14" s="41" t="n">
         <v>545.92</v>
       </c>
-      <c r="J14" s="44" t="n">
+      <c r="J14" s="41" t="n">
         <v>614.16</v>
       </c>
-      <c r="K14" s="44" t="n">
+      <c r="K14" s="41" t="n">
         <v>716.52</v>
       </c>
-      <c r="L14" s="44" t="n">
+      <c r="L14" s="41" t="n">
         <v>853</v>
       </c>
-      <c r="M14" s="44" t="n">
+      <c r="M14" s="41" t="n">
         <v>1023.6</v>
       </c>
-      <c r="N14" s="44" t="n">
+      <c r="N14" s="41" t="n">
         <v>5766.28</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Fixed Costs</t>
-        </is>
-      </c>
-      <c r="B15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="C15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="D15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="E15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="F15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="G15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="H15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="I15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="J15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="K15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="L15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="M15" s="43" t="n">
-        <v>386.83</v>
-      </c>
-      <c r="N15" s="43" t="n">
-        <v>4641.96</v>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Variable Costs</t>
-        </is>
-      </c>
-      <c r="B16" s="43" t="n">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>Data API Costs</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="C16" s="40" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="D16" s="40" t="n">
+        <v>78</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>78</v>
+      </c>
+      <c r="F16" s="40" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="G16" s="40" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H16" s="40" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>120</v>
+      </c>
+      <c r="J16" s="40" t="n">
+        <v>120</v>
+      </c>
+      <c r="K16" s="40" t="n">
+        <v>120</v>
+      </c>
+      <c r="L16" s="40" t="n">
+        <v>120</v>
+      </c>
+      <c r="M16" s="40" t="n">
+        <v>120</v>
+      </c>
+      <c r="N16" s="40" t="n">
+        <v>1111.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="C17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="D17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="E17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="G17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="H17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="J17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="K17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="M17" s="40" t="n">
+        <v>59</v>
+      </c>
+      <c r="N17" s="40" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>AI &amp; Variable</t>
+        </is>
+      </c>
+      <c r="B18" s="40" t="n">
         <v>0.45</v>
       </c>
-      <c r="C16" s="43" t="n">
+      <c r="C18" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="D16" s="43" t="n">
+      <c r="D18" s="40" t="n">
         <v>0.75</v>
       </c>
-      <c r="E16" s="43" t="n">
+      <c r="E18" s="40" t="n">
         <v>0.75</v>
       </c>
-      <c r="F16" s="43" t="n">
+      <c r="F18" s="40" t="n">
         <v>0.9</v>
       </c>
-      <c r="G16" s="43" t="n">
+      <c r="G18" s="40" t="n">
         <v>1.05</v>
       </c>
-      <c r="H16" s="43" t="n">
+      <c r="H18" s="40" t="n">
         <v>1.2</v>
       </c>
-      <c r="I16" s="43" t="n">
+      <c r="I18" s="40" t="n">
         <v>1.5</v>
       </c>
-      <c r="J16" s="43" t="n">
+      <c r="J18" s="40" t="n">
         <v>1.65</v>
       </c>
-      <c r="K16" s="43" t="n">
+      <c r="K18" s="40" t="n">
         <v>1.95</v>
       </c>
-      <c r="L16" s="43" t="n">
+      <c r="L18" s="40" t="n">
         <v>2.25</v>
       </c>
-      <c r="M16" s="43" t="n">
+      <c r="M18" s="40" t="n">
         <v>2.7</v>
       </c>
-      <c r="N16" s="43" t="n">
+      <c r="N18" s="40" t="n">
         <v>15.75</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="41" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>Fixed Overhead</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="C19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="E19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="F19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="G19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="I19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="J19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="K19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="L19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="M19" s="40" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="N19" s="40" t="n">
+        <v>141.96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>Total Costs</t>
         </is>
       </c>
-      <c r="B17" s="44" t="n">
-        <v>387.28</v>
-      </c>
-      <c r="C17" s="44" t="n">
-        <v>387.43</v>
-      </c>
-      <c r="D17" s="44" t="n">
-        <v>387.58</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>387.58</v>
-      </c>
-      <c r="F17" s="44" t="n">
-        <v>387.73</v>
-      </c>
-      <c r="G17" s="44" t="n">
-        <v>387.88</v>
-      </c>
-      <c r="H17" s="44" t="n">
-        <v>388.03</v>
-      </c>
-      <c r="I17" s="44" t="n">
-        <v>388.33</v>
-      </c>
-      <c r="J17" s="44" t="n">
-        <v>388.48</v>
-      </c>
-      <c r="K17" s="44" t="n">
-        <v>388.78</v>
-      </c>
-      <c r="L17" s="44" t="n">
-        <v>389.08</v>
-      </c>
-      <c r="M17" s="44" t="n">
-        <v>389.53</v>
-      </c>
-      <c r="N17" s="44" t="n">
-        <v>4657.71</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="B20" s="41" t="n">
+        <v>102.48</v>
+      </c>
+      <c r="C20" s="41" t="n">
+        <v>111.03</v>
+      </c>
+      <c r="D20" s="41" t="n">
+        <v>149.58</v>
+      </c>
+      <c r="E20" s="41" t="n">
+        <v>149.58</v>
+      </c>
+      <c r="F20" s="41" t="n">
+        <v>158.13</v>
+      </c>
+      <c r="G20" s="41" t="n">
+        <v>166.68</v>
+      </c>
+      <c r="H20" s="41" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="I20" s="41" t="n">
+        <v>192.33</v>
+      </c>
+      <c r="J20" s="41" t="n">
+        <v>192.48</v>
+      </c>
+      <c r="K20" s="41" t="n">
+        <v>192.78</v>
+      </c>
+      <c r="L20" s="41" t="n">
+        <v>193.08</v>
+      </c>
+      <c r="M20" s="41" t="n">
+        <v>193.53</v>
+      </c>
+      <c r="N20" s="41" t="n">
+        <v>1976.91</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>Net Profit/Loss</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n">
-        <v>-216.68</v>
-      </c>
-      <c r="C19" s="27" t="n">
-        <v>-182.71</v>
-      </c>
-      <c r="D19" s="27" t="n">
-        <v>-148.74</v>
-      </c>
-      <c r="E19" s="27" t="n">
-        <v>-114.62</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>-80.65000000000001</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>-12.56</v>
-      </c>
-      <c r="H19" s="31" t="n">
-        <v>55.53</v>
-      </c>
-      <c r="I19" s="31" t="n">
-        <v>157.59</v>
-      </c>
-      <c r="J19" s="31" t="n">
-        <v>225.68</v>
-      </c>
-      <c r="K19" s="31" t="n">
-        <v>327.74</v>
-      </c>
-      <c r="L19" s="31" t="n">
-        <v>463.92</v>
-      </c>
-      <c r="M19" s="31" t="n">
-        <v>634.0700000000001</v>
-      </c>
-      <c r="N19" s="31" t="n">
-        <v>1108.57</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="B22" s="25" t="n">
+        <v>68.12</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>89.26000000000001</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>123.38</v>
+      </c>
+      <c r="F22" s="25" t="n">
+        <v>148.95</v>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>208.64</v>
+      </c>
+      <c r="H22" s="25" t="n">
+        <v>268.33</v>
+      </c>
+      <c r="I22" s="25" t="n">
+        <v>353.59</v>
+      </c>
+      <c r="J22" s="25" t="n">
+        <v>421.68</v>
+      </c>
+      <c r="K22" s="25" t="n">
+        <v>523.74</v>
+      </c>
+      <c r="L22" s="25" t="n">
+        <v>659.92</v>
+      </c>
+      <c r="M22" s="25" t="n">
+        <v>830.0700000000001</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <v>3789.37</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>Cumulative P/L</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n">
-        <v>-216.68</v>
-      </c>
-      <c r="C20" s="45" t="n">
-        <v>-399.39</v>
-      </c>
-      <c r="D20" s="45" t="n">
-        <v>-548.13</v>
-      </c>
-      <c r="E20" s="45" t="n">
-        <v>-662.75</v>
-      </c>
-      <c r="F20" s="45" t="n">
-        <v>-743.4</v>
-      </c>
-      <c r="G20" s="45" t="n">
-        <v>-755.96</v>
-      </c>
-      <c r="H20" s="45" t="n">
-        <v>-700.4299999999999</v>
-      </c>
-      <c r="I20" s="45" t="n">
-        <v>-542.84</v>
-      </c>
-      <c r="J20" s="45" t="n">
-        <v>-317.16</v>
-      </c>
-      <c r="K20" s="45" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="L20" s="45" t="n">
-        <v>474.5</v>
-      </c>
-      <c r="M20" s="45" t="n">
-        <v>1108.57</v>
-      </c>
-      <c r="N20" s="45" t="n">
-        <v>-3293.09</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="B23" s="42" t="n">
+        <v>68.12</v>
+      </c>
+      <c r="C23" s="42" t="n">
+        <v>161.81</v>
+      </c>
+      <c r="D23" s="42" t="n">
+        <v>251.07</v>
+      </c>
+      <c r="E23" s="42" t="n">
+        <v>374.45</v>
+      </c>
+      <c r="F23" s="42" t="n">
+        <v>523.4</v>
+      </c>
+      <c r="G23" s="42" t="n">
+        <v>732.04</v>
+      </c>
+      <c r="H23" s="42" t="n">
+        <v>1000.37</v>
+      </c>
+      <c r="I23" s="42" t="n">
+        <v>1353.96</v>
+      </c>
+      <c r="J23" s="42" t="n">
+        <v>1775.64</v>
+      </c>
+      <c r="K23" s="42" t="n">
+        <v>2299.38</v>
+      </c>
+      <c r="L23" s="42" t="n">
+        <v>2959.3</v>
+      </c>
+      <c r="M23" s="42" t="n">
+        <v>3789.37</v>
+      </c>
+      <c r="N23" s="42" t="n">
+        <v>15288.91</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>Operating Margin</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n">
-        <v>-1.27010550996483</v>
-      </c>
-      <c r="C21" s="46" t="n">
-        <v>-0.8924872997264559</v>
-      </c>
-      <c r="D21" s="46" t="n">
-        <v>-0.6227600066990455</v>
-      </c>
-      <c r="E21" s="46" t="n">
-        <v>-0.4199150058616647</v>
-      </c>
-      <c r="F21" s="46" t="n">
-        <v>-0.2626351439364334</v>
-      </c>
-      <c r="G21" s="46" t="n">
-        <v>-0.03346477672386231</v>
-      </c>
-      <c r="H21" s="46" t="n">
-        <v>0.1251916313463793</v>
-      </c>
-      <c r="I21" s="46" t="n">
-        <v>0.2886686694021102</v>
-      </c>
-      <c r="J21" s="46" t="n">
-        <v>0.3674612478832878</v>
-      </c>
-      <c r="K21" s="46" t="n">
-        <v>0.4574052364204768</v>
-      </c>
-      <c r="L21" s="46" t="n">
-        <v>0.5438686987104338</v>
-      </c>
-      <c r="M21" s="46" t="n">
-        <v>0.6194509574052364</v>
-      </c>
-      <c r="N21" s="46" t="n">
-        <v>0.1922504630368279</v>
+      <c r="B24" s="43" t="n">
+        <v>0.3992966002344666</v>
+      </c>
+      <c r="C24" s="43" t="n">
+        <v>0.4576494724501758</v>
+      </c>
+      <c r="D24" s="43" t="n">
+        <v>0.3737229944732876</v>
+      </c>
+      <c r="E24" s="43" t="n">
+        <v>0.4520076201641267</v>
+      </c>
+      <c r="F24" s="43" t="n">
+        <v>0.485052754982415</v>
+      </c>
+      <c r="G24" s="43" t="n">
+        <v>0.5558989662154961</v>
+      </c>
+      <c r="H24" s="43" t="n">
+        <v>0.6049463432230138</v>
+      </c>
+      <c r="I24" s="43" t="n">
+        <v>0.6476956330597889</v>
+      </c>
+      <c r="J24" s="43" t="n">
+        <v>0.6865963266901134</v>
+      </c>
+      <c r="K24" s="43" t="n">
+        <v>0.7309495896834701</v>
+      </c>
+      <c r="L24" s="43" t="n">
+        <v>0.7736459554513482</v>
+      </c>
+      <c r="M24" s="43" t="n">
+        <v>0.8109320046893318</v>
+      </c>
+      <c r="N24" s="43" t="n">
+        <v>0.6571602488953017</v>
       </c>
     </row>
   </sheetData>
@@ -5035,7 +8236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008B5CF6"/>
@@ -5045,17 +8246,17 @@
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>3-Year Annual Projection</t>
+          <t>3-Year Annual Projection (Computed)</t>
         </is>
       </c>
     </row>
@@ -5068,34 +8269,34 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Year 1 (avg 30 subs)</t>
+          <t>Year 1 (5→50)</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Year 2 (avg 150 subs)</t>
+          <t>Year 2 (50→250)</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Year 3 (avg 500 subs)</t>
+          <t>Year 3 (250→800)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Avg Paid Subscribers</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="n">
+          <t>Ending Paid Subscribers</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="D4" s="26" t="n">
-        <v>500</v>
+      <c r="C4" s="21" t="n">
+        <v>128</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>426</v>
       </c>
     </row>
     <row r="5">
@@ -5107,14 +8308,14 @@
           <t>Annual Gross Revenue</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
-        <v>13320</v>
-      </c>
-      <c r="C6" s="47" t="n">
-        <v>66600</v>
-      </c>
-      <c r="D6" s="47" t="n">
-        <v>222000</v>
+      <c r="B6" s="11" t="n">
+        <v>6251</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>37212</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>146850</v>
       </c>
     </row>
     <row r="7">
@@ -5123,14 +8324,14 @@
           <t>Payment Processing Fees</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
-        <v>-1037</v>
-      </c>
-      <c r="C7" s="48" t="n">
-        <v>-5184</v>
-      </c>
-      <c r="D7" s="48" t="n">
-        <v>-17280</v>
+      <c r="B7" s="44" t="n">
+        <v>-485</v>
+      </c>
+      <c r="C7" s="44" t="n">
+        <v>-2887</v>
+      </c>
+      <c r="D7" s="44" t="n">
+        <v>-11394</v>
       </c>
     </row>
     <row r="8">
@@ -5139,14 +8340,14 @@
           <t>Annual Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
-        <v>12283</v>
-      </c>
-      <c r="C8" s="49" t="n">
-        <v>61416</v>
-      </c>
-      <c r="D8" s="49" t="n">
-        <v>204720</v>
+      <c r="B8" s="18" t="n">
+        <v>5766</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>34325</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>135456</v>
       </c>
     </row>
     <row r="9">
@@ -5155,65 +8356,65 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Infrastructure (fixed)</t>
-        </is>
-      </c>
-      <c r="B10" s="47" t="n">
-        <v>-4642</v>
-      </c>
-      <c r="C10" s="47" t="n">
-        <v>-6444</v>
-      </c>
-      <c r="D10" s="47" t="n">
-        <v>-12204</v>
+          <t>Data API Costs</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="n">
+        <v>-1111</v>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>-2661</v>
+      </c>
+      <c r="D10" s="45" t="n">
+        <v>-5188</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Variable API Costs</t>
-        </is>
-      </c>
-      <c r="B11" s="48" t="n">
-        <v>-60</v>
-      </c>
-      <c r="C11" s="48" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="D11" s="48" t="n">
-        <v>-10080</v>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="n">
+        <v>-708</v>
+      </c>
+      <c r="C11" s="44" t="n">
+        <v>-708</v>
+      </c>
+      <c r="D11" s="44" t="n">
+        <v>-3228</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Anthropic AI</t>
-        </is>
-      </c>
-      <c r="B12" s="47" t="n">
-        <v>-54</v>
-      </c>
-      <c r="C12" s="47" t="n">
-        <v>-270</v>
-      </c>
-      <c r="D12" s="47" t="n">
-        <v>-900</v>
+          <t>AI &amp; Variable</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="n">
+        <v>-16</v>
+      </c>
+      <c r="C12" s="45" t="n">
+        <v>-91</v>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>-377</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>RevenueCat (1% mobile MTR)</t>
-        </is>
-      </c>
-      <c r="B13" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="48" t="n">
-        <v>-184</v>
-      </c>
-      <c r="D13" s="48" t="n">
-        <v>-614</v>
+          <t>Fixed Overhead</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="n">
+        <v>-142</v>
+      </c>
+      <c r="C13" s="44" t="n">
+        <v>-142</v>
+      </c>
+      <c r="D13" s="44" t="n">
+        <v>-142</v>
       </c>
     </row>
     <row r="14">
@@ -5222,14 +8423,14 @@
           <t>Total Operating Costs</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
-        <v>-4756</v>
-      </c>
-      <c r="C14" s="49" t="n">
-        <v>-8038</v>
-      </c>
-      <c r="D14" s="49" t="n">
-        <v>-23798</v>
+      <c r="B14" s="46" t="n">
+        <v>-1977</v>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>-3602</v>
+      </c>
+      <c r="D14" s="46" t="n">
+        <v>-8934</v>
       </c>
     </row>
     <row r="15">
@@ -5241,14 +8442,14 @@
           <t>Annual Operating Profit</t>
         </is>
       </c>
-      <c r="B16" s="50" t="n">
-        <v>7527</v>
-      </c>
-      <c r="C16" s="50" t="n">
-        <v>53378</v>
-      </c>
-      <c r="D16" s="50" t="n">
-        <v>180922</v>
+      <c r="B16" s="47" t="n">
+        <v>3789</v>
+      </c>
+      <c r="C16" s="47" t="n">
+        <v>30723</v>
+      </c>
+      <c r="D16" s="47" t="n">
+        <v>126522</v>
       </c>
     </row>
     <row r="17">
@@ -5258,13 +8459,13 @@
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>0.613</v>
+        <v>0.6571602488953016</v>
       </c>
       <c r="C17" s="14" t="n">
-        <v>0.869</v>
+        <v>0.8950724142833503</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>0.884</v>
+        <v>0.9340445338869187</v>
       </c>
     </row>
     <row r="18">
@@ -5276,14 +8477,14 @@
           <t>Monthly Avg Profit</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n">
-        <v>627</v>
-      </c>
-      <c r="C19" s="49" t="n">
-        <v>4448</v>
-      </c>
-      <c r="D19" s="49" t="n">
-        <v>15077</v>
+      <c r="B19" s="46" t="n">
+        <v>316</v>
+      </c>
+      <c r="C19" s="46" t="n">
+        <v>2560</v>
+      </c>
+      <c r="D19" s="46" t="n">
+        <v>10544</v>
       </c>
     </row>
   </sheetData>
@@ -5294,7 +8495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00EF4444"/>
@@ -5353,9 +8554,9 @@
           <t>RentCast price increase</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
-        <is>
-          <t>High — 51% of costs</t>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>High — 51% of base costs</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -5365,7 +8566,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Optimize caching; negotiate volume pricing</t>
+          <t>Optimize caching; negotiate volume</t>
         </is>
       </c>
     </row>
@@ -5375,7 +8576,7 @@
           <t>AXESSO/Zillow API discontinued</t>
         </is>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
         <is>
           <t>Critical — lose Zestimate</t>
         </is>
@@ -5397,7 +8598,7 @@
           <t>RapidAPI plan changes</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Medium — lose Redfin/Realtor</t>
         </is>
@@ -5419,7 +8620,7 @@
           <t>Apple rejects SBP (15%→30%)</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Medium — mobile margin drops</t>
         </is>
@@ -5441,7 +8642,7 @@
           <t>Low annual conversion rate</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Medium — lower blended ARPU</t>
         </is>
@@ -5453,7 +8654,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Incentivize annual with deeper discount</t>
+          <t>Incentivize annual w/ deeper discount</t>
         </is>
       </c>
     </row>
@@ -5463,7 +8664,7 @@
           <t>High churn (&gt;10%/mo)</t>
         </is>
       </c>
-      <c r="B10" s="51" t="inlineStr">
+      <c r="B10" s="48" t="inlineStr">
         <is>
           <t>High — never reach scale</t>
         </is>
@@ -5485,7 +8686,7 @@
           <t>Free tier API abuse</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Medium — consumes paid quota</t>
         </is>
@@ -5507,7 +8708,7 @@
           <t>Competitor with free tier</t>
         </is>
       </c>
-      <c r="B12" s="51" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>High — pricing pressure</t>
         </is>
@@ -5569,7 +8770,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D16" s="51" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>P0 — Immediate</t>
         </is>
@@ -5591,7 +8792,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D17" s="33" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>P1 — Next sprint</t>
         </is>
@@ -5613,7 +8814,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5635,7 +8836,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D19" s="49" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5657,7 +8858,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="D20" s="49" t="inlineStr">
         <is>
           <t>P2 — When applicable</t>
         </is>

--- a/docs/DealGapIQ_Financial_Proforma.xlsx
+++ b/docs/DealGapIQ_Financial_Proforma.xlsx
@@ -389,7 +389,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Profitability'!$A$8:$A$28</f>
+              <f>'Profitability'!$A$7:$A$28</f>
             </numRef>
           </cat>
           <val>
@@ -502,7 +502,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Profitability'!$A$8:$A$28</f>
+              <f>'Profitability'!$A$7:$A$28</f>
             </numRef>
           </cat>
           <val>
@@ -526,7 +526,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Profitability'!$A$8:$A$28</f>
+              <f>'Profitability'!$A$7:$A$28</f>
             </numRef>
           </cat>
           <val>
@@ -550,7 +550,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Profitability'!$A$8:$A$28</f>
+              <f>'Profitability'!$A$7:$A$28</f>
             </numRef>
           </cat>
           <val>
@@ -574,7 +574,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Profitability'!$A$8:$A$28</f>
+              <f>'Profitability'!$A$7:$A$28</f>
             </numRef>
           </cat>
           <val>
@@ -1350,7 +1350,7 @@
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Primary Cost Driver</t>
+          <t>Top Cost @ 100 Subs</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>RentCast (51%)</t>
+          <t>RentCast (46%)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>~48–80 subs</t>
+          <t>~100 subs (RapidAPI — Redfin)</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="B5" s="48" t="inlineStr">
         <is>
-          <t>High — 51% of base costs</t>
+          <t>High — 46% of costs @ 100 subs</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
